--- a/用卷/1990.xlsx
+++ b/用卷/1990.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\高考用卷\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C1580E0-8488-4B89-9D62-452E3F7A3188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{022F31F8-FBC0-4B9C-BBAD-C6531088A75B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="61">
   <si>
     <t>年份</t>
   </si>
@@ -206,11 +206,31 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>全国卷,上海卷,</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>分科卷数统计</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>英语为MET,政治为吉林卷,其他科目为全国卷</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>英语为MET,政治为皖赣卷,其他科目为全国卷</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>北师大政治教材试点区</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>政治为北师大卷,英语为MET,其他科目为全国卷</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>全国卷,北师大卷,吉林卷,上海卷,皖赣卷,广东卷</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>全国卷</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -673,11 +693,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="53.25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="54.625" bestFit="1" customWidth="1"/>
   </cols>
@@ -705,83 +725,83 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="18">
-        <v>1990</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="A3" s="11">
+        <v>1990</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="18"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="18">
+        <v>1990</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="D3" s="9"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
-        <v>1990</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>44</v>
-      </c>
       <c r="C4" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="15"/>
+      <c r="D4" s="9"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>1990</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>38</v>
+      <c r="B5" s="5" t="s">
+        <v>44</v>
       </c>
       <c r="C5" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="9"/>
+      <c r="D5" s="15"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>1990</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="C6" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="10"/>
+      <c r="D6" s="9"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>1990</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="D7" s="8"/>
+      <c r="D7" s="10"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>1990</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>43</v>
+      <c r="B8" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="C8" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="9"/>
+      <c r="D8" s="8"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>1990</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>6</v>
+      <c r="B9" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="C9" s="18" t="s">
         <v>47</v>
@@ -793,7 +813,7 @@
         <v>1990</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C10" s="18" t="s">
         <v>47</v>
@@ -805,79 +825,79 @@
         <v>1990</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="9"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>1990</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" s="10"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="11">
-        <v>1990</v>
-      </c>
-      <c r="B12" s="18" t="s">
+      <c r="C12" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="10"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="11">
+        <v>1990</v>
+      </c>
+      <c r="B13" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C13" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D12" s="18"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="1">
-        <v>1990</v>
-      </c>
-      <c r="B13" s="5" t="s">
+      <c r="D13" s="18"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>1990</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="17"/>
-    </row>
-    <row r="14" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="1">
-        <v>1990</v>
-      </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="17"/>
+    </row>
+    <row r="15" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>1990</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" s="17"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="1">
-        <v>1990</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>45</v>
-      </c>
       <c r="C15" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="12"/>
+      <c r="D15" s="17"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>1990</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" s="9"/>
+      <c r="B16" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="12"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>1990</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C17" s="18" t="s">
         <v>47</v>
@@ -889,10 +909,10 @@
         <v>1990</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>47</v>
+        <v>10</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>56</v>
       </c>
       <c r="D18" s="9"/>
     </row>
@@ -901,7 +921,7 @@
         <v>1990</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C19" s="18" t="s">
         <v>47</v>
@@ -913,103 +933,103 @@
         <v>1990</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C20" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="D20" s="10"/>
+      <c r="D20" s="9"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>1990</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="D21" s="17"/>
+        <v>47</v>
+      </c>
+      <c r="D21" s="10"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>1990</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="D22" s="10"/>
+        <v>49</v>
+      </c>
+      <c r="D22" s="17"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>1990</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C23" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="D23" s="8"/>
+      <c r="D23" s="10"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>1990</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C24" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="D24" s="9"/>
+      <c r="D24" s="8"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>1990</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C25" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="D25" s="13"/>
+      <c r="D25" s="9"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>1990</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C26" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="D26" s="9"/>
+      <c r="D26" s="13"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>1990</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C27" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="D27" s="11"/>
+      <c r="D27" s="9"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>1990</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C28" s="18" t="s">
         <v>47</v>
@@ -1020,127 +1040,127 @@
       <c r="A29" s="1">
         <v>1990</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>41</v>
+      <c r="B29" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="C29" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="D29" s="9"/>
+      <c r="D29" s="11"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>1990</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>22</v>
+      <c r="B30" s="5" t="s">
+        <v>41</v>
       </c>
       <c r="C30" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="D30" s="8"/>
+      <c r="D30" s="9"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>1990</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="D31" s="8"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>1990</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C31" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="D31" s="11"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="9">
-        <v>1990</v>
-      </c>
-      <c r="B32" s="9" t="s">
+      <c r="C32" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="D32" s="11"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" s="9">
+        <v>1990</v>
+      </c>
+      <c r="B33" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C32" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="D32" s="9"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="14"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
+      <c r="C33" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="D33" s="9"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="B34" s="21"/>
-      <c r="C34" s="21"/>
-      <c r="D34" s="7"/>
+      <c r="A34" s="14"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>27</v>
-      </c>
+      <c r="A35" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
       <c r="D35" s="7"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B36" s="4">
-        <v>3</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>51</v>
+        <v>25</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="D36" s="7"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B37" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D37" s="7"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B38" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D38" s="7"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B39" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D39" s="7"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B40" s="4">
         <v>3</v>
@@ -1148,59 +1168,71 @@
       <c r="C40" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D40" s="19"/>
+      <c r="D40" s="7"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B41" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D41" s="7"/>
+        <v>51</v>
+      </c>
+      <c r="D41" s="19"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B42" s="4">
-        <v>2</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>53</v>
+        <v>1</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="D42" s="7"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B43" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D43" s="7"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B44" s="4">
+        <v>6</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D44" s="7"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A45" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B44" s="4">
-        <v>2</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="D44" s="7"/>
+      <c r="B45" s="4">
+        <v>1</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D45" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:C35"/>
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
